--- a/excel/Kommune_FAST_Finansiell_Modell_2026.xlsx
+++ b/excel/Kommune_FAST_Finansiell_Modell_2026.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 6cc492b506cb6811ce1b8a96195ea7f389fb905a31b40c31bdef97ac6e673a5d</t>
+          <t>SHA-256: 29ab257418f60acbfb5680d376995072f4141565710581df2b73590a6bb4166f</t>
         </is>
       </c>
     </row>

--- a/excel/Kommune_FAST_Finansiell_Modell_2026.xlsx
+++ b/excel/Kommune_FAST_Finansiell_Modell_2026.xlsx
@@ -782,7 +782,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>SHA-256: 29ab257418f60acbfb5680d376995072f4141565710581df2b73590a6bb4166f</t>
+          <t>SHA-256: 742c47dca32dc3aebbd9e791e9f8bd6b386144572394c33149164ef06b43fb44</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>14.10.2026</t>
+          <t>18.10.2026</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
@@ -2204,7 +2204,7 @@
         <v>4890000</v>
       </c>
       <c r="F6" s="25">
-        <f>E6-D6</f>
+        <f>D6-E6</f>
         <v/>
       </c>
       <c r="G6" s="26">
@@ -2223,7 +2223,7 @@
         <v/>
       </c>
       <c r="K6" s="25">
-        <f>J6-(D6*2)</f>
+        <f>(D6*2)-J6</f>
         <v/>
       </c>
     </row>
@@ -2243,7 +2243,7 @@
         <v>1820000</v>
       </c>
       <c r="F7" s="25">
-        <f>E7-D7</f>
+        <f>D7-E7</f>
         <v/>
       </c>
       <c r="G7" s="26">
@@ -2262,7 +2262,7 @@
         <v/>
       </c>
       <c r="K7" s="25">
-        <f>J7-(D7*2)</f>
+        <f>(D7*2)-J7</f>
         <v/>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
         <v>436000</v>
       </c>
       <c r="F8" s="25">
-        <f>E8-D8</f>
+        <f>D8-E8</f>
         <v/>
       </c>
       <c r="G8" s="26">
@@ -2301,7 +2301,7 @@
         <v/>
       </c>
       <c r="K8" s="25">
-        <f>J8-(D8*2)</f>
+        <f>(D8*2)-J8</f>
         <v/>
       </c>
     </row>
@@ -2321,7 +2321,7 @@
         <v>184000</v>
       </c>
       <c r="F9" s="25">
-        <f>E9-D9</f>
+        <f>D9-E9</f>
         <v/>
       </c>
       <c r="G9" s="26">
@@ -2340,7 +2340,7 @@
         <v/>
       </c>
       <c r="K9" s="25">
-        <f>J9-(D9*2)</f>
+        <f>(D9*2)-J9</f>
         <v/>
       </c>
     </row>
@@ -2360,7 +2360,7 @@
         <v>-410000</v>
       </c>
       <c r="F10" s="25">
-        <f>E10-D10</f>
+        <f>D10-E10</f>
         <v/>
       </c>
       <c r="G10" s="26">
@@ -2379,7 +2379,7 @@
         <v/>
       </c>
       <c r="K10" s="25">
-        <f>J10-(D10*2)</f>
+        <f>(D10*2)-J10</f>
         <v/>
       </c>
     </row>
@@ -2399,7 +2399,7 @@
         <v>780000</v>
       </c>
       <c r="F11" s="25">
-        <f>E11-D11</f>
+        <f>D11-E11</f>
         <v/>
       </c>
       <c r="G11" s="26">
@@ -2418,7 +2418,7 @@
         <v/>
       </c>
       <c r="K11" s="25">
-        <f>J11-(D11*2)</f>
+        <f>(D11*2)-J11</f>
         <v/>
       </c>
     </row>
